--- a/AAAGameData/DataTables/Hero/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Hero/SkillTable.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Avenge\AAAGameData\DataTables\Hero\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
@@ -12,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$R$1:$R$28</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>#</t>
   </si>
@@ -185,34 +190,49 @@
     <t>Skill_Desc_JustPassingBy</t>
   </si>
   <si>
-    <t>Skill_BladeDance</t>
-  </si>
-  <si>
-    <t>刀舞</t>
-  </si>
-  <si>
-    <t>技能期间，英雄+{0}攻速。</t>
-  </si>
-  <si>
-    <t>Skill_Name_BladeDance</t>
-  </si>
-  <si>
-    <t>Skill_Desc_BladeDance</t>
-  </si>
-  <si>
-    <t>Skill_FireDrill</t>
-  </si>
-  <si>
-    <t>消防演习</t>
-  </si>
-  <si>
-    <t>在目标地点产生一阵浓烟，浓烟存在期间，其范围内的敌人受到致盲效果，攻击有{0}%的概率落空。</t>
-  </si>
-  <si>
-    <t>Skill_Name_FireDrill</t>
-  </si>
-  <si>
-    <t>Skill_Desc_FireDrill</t>
+    <t>Skill_InsatiableThirst</t>
+  </si>
+  <si>
+    <t>饥渴难耐</t>
+  </si>
+  <si>
+    <t>技能期间，英雄+{0}攻速，并获得{1}%攻击吸血。</t>
+  </si>
+  <si>
+    <t>50,25</t>
+  </si>
+  <si>
+    <t>20,10</t>
+  </si>
+  <si>
+    <t>Skill_Name_InsatiableThirst</t>
+  </si>
+  <si>
+    <t>Skill_Desc_InsatiableThirst</t>
+  </si>
+  <si>
+    <t>Skill_ForgedInFire</t>
+  </si>
+  <si>
+    <t>火线淬炼</t>
+  </si>
+  <si>
+    <t>附近每有1个敌方单位死亡，英雄便永久+{0}%攻击，至多叠加{1}层。</t>
+  </si>
+  <si>
+    <t>1,50</t>
+  </si>
+  <si>
+    <t>0.5,20</t>
+  </si>
+  <si>
+    <t>SkillType.Passive</t>
+  </si>
+  <si>
+    <t>Skill_Name_ForgedInFire</t>
+  </si>
+  <si>
+    <t>Skill_Desc_ForgedInFire</t>
   </si>
   <si>
     <t>Skill_UrgentRequest</t>
@@ -221,7 +241,13 @@
     <t>临时需求</t>
   </si>
   <si>
-    <t>在目标点部署{0}名实习生，实习生有寿命限制。</t>
+    <t>在目标点部署{0}名实习生，它们获得+{1}攻击，+{2}生命上限，且不占用频段。</t>
+  </si>
+  <si>
+    <t>8,3,15</t>
+  </si>
+  <si>
+    <t>2,2,10</t>
   </si>
   <si>
     <t>Skill_Name_UrgentRequest</t>
@@ -230,43 +256,34 @@
     <t>Skill_Desc_UrgentRequest</t>
   </si>
   <si>
-    <t>Skill_LightLoad</t>
-  </si>
-  <si>
-    <t>轻装上阵</t>
-  </si>
-  <si>
-    <t>英雄+{0}%移速。</t>
-  </si>
-  <si>
-    <t>SkillType.Passive</t>
-  </si>
-  <si>
-    <t>Skill_Name_LightLoad</t>
-  </si>
-  <si>
-    <t>Skill_Desc_LightLoad</t>
-  </si>
-  <si>
-    <t>Skill_Disarm</t>
-  </si>
-  <si>
-    <t>卸除武装</t>
-  </si>
-  <si>
-    <t>对敌方单位造成伤害时，使其在一段时间内-{0}攻击、-{1}护甲。（不叠加）</t>
-  </si>
-  <si>
-    <t>5,2</t>
-  </si>
-  <si>
-    <t>1,0.5</t>
-  </si>
-  <si>
-    <t>Skill_Name_Disarm</t>
-  </si>
-  <si>
-    <t>Skill_Desc_Disarm</t>
+    <t>Skill_ExpressDelivery</t>
+  </si>
+  <si>
+    <t>特急派送</t>
+  </si>
+  <si>
+    <t>向目标地点突进，对终点附近的敌人造成{0}伤害和眩晕。（备注：可以跨越高坡上下，但中间不能有非陆地格）</t>
+  </si>
+  <si>
+    <t>Skill_Name_ExpressDelivery</t>
+  </si>
+  <si>
+    <t>Skill_Desc_ExpressDelivery</t>
+  </si>
+  <si>
+    <t>Skill_RiotArmor</t>
+  </si>
+  <si>
+    <t>防暴装甲</t>
+  </si>
+  <si>
+    <t>英雄+{0}护甲。</t>
+  </si>
+  <si>
+    <t>Skill_Name_RiotArmor</t>
+  </si>
+  <si>
+    <t>Skill_Desc_RiotArmor</t>
   </si>
   <si>
     <t>Skill_GiantSlayer</t>
@@ -275,7 +292,7 @@
     <t>巨人杀手</t>
   </si>
   <si>
-    <t>英雄的普通攻击额外造成敌人当前生命{0}%的伤害。</t>
+    <t>英雄攻击时，额外造成敌人当前生命{0}%的伤害。</t>
   </si>
   <si>
     <t>Skill_Name_GiantSlayer</t>
@@ -837,163 +854,163 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1318,23 +1335,23 @@
   <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.8333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="10" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="13" max="16" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="17" max="19" width="16.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="23.25" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.1583333333333" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="2.5" customWidth="1" style="1"/>
+    <col min="2" max="2" width="7" customWidth="1" style="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1" style="1"/>
+    <col min="4" max="4" width="10" customWidth="1" style="1"/>
+    <col min="5" max="5" width="19.8333333333333" customWidth="1" style="1"/>
+    <col min="6" max="6" width="17.3333333333333" customWidth="1" style="1"/>
+    <col min="7" max="10" width="20.8333333333333" customWidth="1" style="1"/>
+    <col min="11" max="11" width="16.75" customWidth="1" style="1"/>
+    <col min="12" max="12" width="17.3333333333333" customWidth="1" style="1"/>
+    <col min="13" max="16" width="20.8333333333333" customWidth="1" style="1"/>
+    <col min="17" max="19" width="16.75" customWidth="1" style="1"/>
+    <col min="20" max="20" width="23.25" customWidth="1" style="1"/>
+    <col min="21" max="21" width="19.1583333333333" customWidth="1" style="1"/>
+    <col min="22" max="16384" width="8.875" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1382,7 @@
       </c>
       <c r="U1" s="2"/>
     </row>
-    <row r="2" ht="28.75" spans="1:21">
+    <row r="2" ht="28.75">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1426,7 +1443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1487,7 +1504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.75" spans="1:21">
+    <row r="4" ht="28.75">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1567,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" ht="56.75" spans="1:21">
+    <row r="5" ht="56.75">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -1607,7 +1624,7 @@
       </c>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" ht="28.75" spans="1:21">
+    <row r="6" ht="42.75">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
@@ -1621,8 +1638,8 @@
       <c r="E6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2">
-        <v>80</v>
+      <c r="F6" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1635,13 +1652,13 @@
       <c r="K6" s="2">
         <v>8</v>
       </c>
-      <c r="L6" s="3">
-        <v>30</v>
+      <c r="L6" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" s="2">
         <v>1</v>
@@ -1651,89 +1668,77 @@
         <v>48</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" ht="74" customHeight="1" spans="1:21">
+    <row r="7" ht="74" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="2">
-        <v>50</v>
-      </c>
-      <c r="G7" s="2">
-        <v>700</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="2"/>
       <c r="H7" s="2">
-        <v>250</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2">
-        <v>8</v>
-      </c>
-      <c r="L7" s="2">
-        <v>10</v>
+        <v>500</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2">
-        <v>30</v>
-      </c>
-      <c r="O7" s="2">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" ht="42.75" spans="1:21">
+    <row r="8" ht="56.75">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
+        <v>68</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G8" s="2">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1743,126 +1748,140 @@
       <c r="K8" s="2">
         <v>10</v>
       </c>
-      <c r="L8" s="2">
-        <v>2</v>
+      <c r="L8" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="2">
-        <v>1</v>
-      </c>
+      <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2" t="s">
         <v>48</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" ht="28.75" spans="1:21">
+    <row r="9" ht="70.75">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F9" s="2">
-        <v>16</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="G9" s="2">
+        <v>600</v>
+      </c>
+      <c r="H9" s="2">
+        <v>250</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2</v>
+      </c>
+      <c r="K9" s="2">
+        <v>10</v>
+      </c>
       <c r="L9" s="2">
-        <v>12</v>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="M9" s="2">
+        <v>50</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.5</v>
+      </c>
       <c r="R9" s="2" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" ht="56.75" spans="1:21">
+    <row r="10">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2">
-        <v>3</v>
-      </c>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2" t="s">
-        <v>76</v>
+      <c r="L10" s="2">
+        <v>4</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="2">
-        <v>1</v>
-      </c>
+      <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" ht="42.75" spans="1:21">
+    <row r="11" ht="42.75">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F11" s="2">
         <v>8</v>
@@ -1881,29 +1900,29 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" ht="42.75" spans="1:21">
+    <row r="12" ht="42.75">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F12" s="2"/>
       <c r="H12" s="2">
@@ -1934,29 +1953,29 @@
         <v>48</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" ht="42.75" spans="1:21">
+    <row r="13" ht="42.75">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1964,7 +1983,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -1972,29 +1991,29 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" ht="42.75" spans="1:21">
+    <row r="14" ht="42.75">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F14" s="2">
         <v>30</v>
@@ -2017,17 +2036,17 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2050,7 +2069,7 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2073,7 +2092,7 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2096,7 +2115,7 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2119,7 +2138,7 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2142,7 +2161,7 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2165,7 +2184,7 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2188,7 +2207,7 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2211,7 +2230,7 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2234,7 +2253,7 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2257,7 +2276,7 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2280,7 +2299,7 @@
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2303,7 +2322,7 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2326,7 +2345,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>

--- a/AAAGameData/DataTables/Hero/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Hero/SkillTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="6790" windowHeight="5630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$R$1:$R$28</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="105">
   <si>
     <t>#</t>
   </si>
@@ -316,7 +316,7 @@
     <t>Skill_Desc_Injection</t>
   </si>
   <si>
-    <t>Skill_Cheer Squad</t>
+    <t>Skill_CheerSquad</t>
   </si>
   <si>
     <t>啦啦队</t>
@@ -854,163 +854,163 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="0">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1335,23 +1335,23 @@
   <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
-    <col min="1" max="1" width="2.5" customWidth="1" style="1"/>
-    <col min="2" max="2" width="7" customWidth="1" style="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1" style="1"/>
-    <col min="4" max="4" width="10" customWidth="1" style="1"/>
-    <col min="5" max="5" width="19.8333333333333" customWidth="1" style="1"/>
-    <col min="6" max="6" width="17.3333333333333" customWidth="1" style="1"/>
-    <col min="7" max="10" width="20.8333333333333" customWidth="1" style="1"/>
-    <col min="11" max="11" width="16.75" customWidth="1" style="1"/>
-    <col min="12" max="12" width="17.3333333333333" customWidth="1" style="1"/>
-    <col min="13" max="16" width="20.8333333333333" customWidth="1" style="1"/>
-    <col min="17" max="19" width="16.75" customWidth="1" style="1"/>
-    <col min="20" max="20" width="23.25" customWidth="1" style="1"/>
-    <col min="21" max="21" width="19.1583333333333" customWidth="1" style="1"/>
-    <col min="22" max="16384" width="8.875" customWidth="1" style="1"/>
+    <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.8333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="7" max="10" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="13" max="16" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="17" max="19" width="16.75" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.1583333333333" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="U1" s="2"/>
     </row>
-    <row r="2" ht="28.75">
+    <row r="2" ht="28.75" spans="1:21">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:21">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.75">
+    <row r="4" ht="28.75" spans="1:21">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" ht="56.75">
+    <row r="5" ht="56.75" spans="1:21">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" ht="42.75">
+    <row r="6" ht="42.75" spans="1:21">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" ht="74" customHeight="1">
+    <row r="7" ht="74" customHeight="1" spans="1:21">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" ht="56.75">
+    <row r="8" ht="56.75" spans="1:21">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" ht="70.75">
+    <row r="9" ht="70.75" spans="1:21">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" ht="28.75" spans="1:21">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
         <v>6</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" ht="42.75">
+    <row r="11" ht="42.75" spans="1:21">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>7</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" ht="42.75">
+    <row r="12" ht="42.75" spans="1:21">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>8</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" ht="42.75">
+    <row r="13" ht="42.75" spans="1:21">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>9</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" ht="42.75">
+    <row r="14" ht="42.75" spans="1:21">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="U14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:21">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2069,7 +2069,7 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:21">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2092,7 +2092,7 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:21">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2115,7 +2115,7 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:21">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2138,7 +2138,7 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:21">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2161,7 +2161,7 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:21">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2184,7 +2184,7 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:21">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2207,7 +2207,7 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:21">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2230,7 +2230,7 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:21">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2253,7 +2253,7 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:21">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2276,7 +2276,7 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:21">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2299,7 +2299,7 @@
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:21">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2322,7 +2322,7 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:21">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2345,7 +2345,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:21">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>

--- a/AAAGameData/DataTables/Hero/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Hero/SkillTable.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$R$1:$R$28</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>#</t>
   </si>
@@ -127,10 +127,10 @@
     <t>1级数值</t>
   </si>
   <si>
-    <t>1级施法距离</t>
-  </si>
-  <si>
-    <t>1级作用范围</t>
+    <t>1级施法距离（格）</t>
+  </si>
+  <si>
+    <t>1级作用范围（格）</t>
   </si>
   <si>
     <t>1级持续时间</t>
@@ -145,10 +145,10 @@
     <t>升级增加数值</t>
   </si>
   <si>
-    <t>升级增加施法距离</t>
-  </si>
-  <si>
-    <t>升级增加作用范围</t>
+    <t>升级增加施法距离（格）</t>
+  </si>
+  <si>
+    <t>升级增加作用范围（格）</t>
   </si>
   <si>
     <t>升级增加持续时间</t>
@@ -1335,23 +1335,23 @@
   <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.8333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="10" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="13" max="16" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="17" max="19" width="16.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="23.25" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.1583333333333" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5" customWidth="1" style="1"/>
+    <col min="2" max="2" width="7" customWidth="1" style="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1" style="1"/>
+    <col min="4" max="4" width="10" customWidth="1" style="1"/>
+    <col min="5" max="5" width="19.8333333333333" customWidth="1" style="1"/>
+    <col min="6" max="6" width="17.3333333333333" customWidth="1" style="1"/>
+    <col min="7" max="10" width="20.8333333333333" customWidth="1" style="1"/>
+    <col min="11" max="11" width="16.75" customWidth="1" style="1"/>
+    <col min="12" max="12" width="17.3333333333333" customWidth="1" style="1"/>
+    <col min="13" max="16" width="20.8333333333333" customWidth="1" style="1"/>
+    <col min="17" max="19" width="16.75" customWidth="1" style="1"/>
+    <col min="20" max="20" width="23.25" customWidth="1" style="1"/>
+    <col min="21" max="21" width="19.1583333333333" customWidth="1" style="1"/>
+    <col min="22" max="16384" width="8.875" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="U1" s="2"/>
     </row>
-    <row r="2" ht="28.75" spans="1:21">
+    <row r="2" ht="28.75">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.75" spans="1:21">
+    <row r="4" ht="28.75">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" ht="56.75" spans="1:21">
+    <row r="5" ht="56.75">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -1585,10 +1585,10 @@
         <v>30</v>
       </c>
       <c r="G5" s="2">
-        <v>700</v>
+        <v>12.6</v>
       </c>
       <c r="H5" s="2">
-        <v>400</v>
+        <v>7.2</v>
       </c>
       <c r="I5" s="2">
         <v>8</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2">
-        <v>50</v>
+        <v>0.9</v>
       </c>
       <c r="O5" s="2">
         <v>2</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" ht="42.75" spans="1:21">
+    <row r="6" ht="42.75">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" ht="74" customHeight="1" spans="1:21">
+    <row r="7" ht="74" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2">
-        <v>100</v>
+        <v>1.8</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" ht="56.75" spans="1:21">
+    <row r="8" ht="56.75">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
@@ -1738,7 +1738,7 @@
         <v>69</v>
       </c>
       <c r="G8" s="2">
-        <v>900</v>
+        <v>16.2</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" ht="70.75" spans="1:21">
+    <row r="9" ht="70.75">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
@@ -1785,10 +1785,10 @@
         <v>40</v>
       </c>
       <c r="G9" s="2">
-        <v>600</v>
+        <v>10.8</v>
       </c>
       <c r="H9" s="2">
-        <v>250</v>
+        <v>4.5</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -1803,10 +1803,10 @@
         <v>20</v>
       </c>
       <c r="M9" s="2">
-        <v>50</v>
+        <v>0.9</v>
       </c>
       <c r="N9" s="2">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="O9" s="2">
         <v>0.5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" ht="28.75" spans="1:21">
+    <row r="10" ht="28.75">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
         <v>6</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" ht="42.75" spans="1:21">
+    <row r="11" ht="42.75">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>7</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" ht="42.75" spans="1:21">
+    <row r="12" ht="42.75">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>8</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F12" s="2"/>
       <c r="H12" s="2">
-        <v>300</v>
+        <v>5.4</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
@@ -1940,7 +1940,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2">
-        <v>50</v>
+        <v>0.9</v>
       </c>
       <c r="O12" s="2">
         <v>1</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" ht="42.75" spans="1:21">
+    <row r="13" ht="42.75">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>9</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" ht="42.75" spans="1:21">
+    <row r="14" ht="42.75">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2">
-        <v>200</v>
+        <v>3.6</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2069,7 +2069,7 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2092,7 +2092,7 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2115,7 +2115,7 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2138,7 +2138,7 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2161,7 +2161,7 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2184,7 +2184,7 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2207,7 +2207,7 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2230,7 +2230,7 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2253,7 +2253,7 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2276,7 +2276,7 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2299,7 +2299,7 @@
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2322,7 +2322,7 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2345,7 +2345,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>

--- a/AAAGameData/DataTables/Hero/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Hero/SkillTable.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="6790" windowHeight="5630"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$R$1:$R$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$T$1:$T$28</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -43,6 +43,9 @@
     <t>建筑表</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>i18n</t>
   </si>
   <si>
@@ -70,6 +73,12 @@
     <t>Lv1Cooldown</t>
   </si>
   <si>
+    <t>WindUp</t>
+  </si>
+  <si>
+    <t>WindDown</t>
+  </si>
+  <si>
     <t>UpgradeIncrementUniqueValues</t>
   </si>
   <si>
@@ -127,10 +136,10 @@
     <t>1级数值</t>
   </si>
   <si>
-    <t>1级施法距离（格）</t>
-  </si>
-  <si>
-    <t>1级作用范围（格）</t>
+    <t>1级施法距离</t>
+  </si>
+  <si>
+    <t>1级作用范围</t>
   </si>
   <si>
     <t>1级持续时间</t>
@@ -142,13 +151,19 @@
     <t>1级冷却时间</t>
   </si>
   <si>
+    <t>技能前摇</t>
+  </si>
+  <si>
+    <t>技能后摇</t>
+  </si>
+  <si>
     <t>升级增加数值</t>
   </si>
   <si>
-    <t>升级增加施法距离（格）</t>
-  </si>
-  <si>
-    <t>升级增加作用范围（格）</t>
+    <t>升级增加施法距离</t>
+  </si>
+  <si>
+    <t>升级增加作用范围</t>
   </si>
   <si>
     <t>升级增加持续时间</t>
@@ -292,7 +307,7 @@
     <t>巨人杀手</t>
   </si>
   <si>
-    <t>英雄攻击时，额外造成敌人当前生命{0}%的伤害。</t>
+    <t>英雄攻击时，额外附加敌方单位当前生命{0}%的伤害。</t>
   </si>
   <si>
     <t>Skill_Name_GiantSlayer</t>
@@ -343,13 +358,28 @@
     <t>整整齐齐</t>
   </si>
   <si>
-    <t>英雄的普通攻击也会对目标附近生命比例更高的单位造成{0}%伤害。</t>
+    <t>英雄的普通攻击也会对目标附近生命比例更高的敌方单位造成{0}%伤害。</t>
   </si>
   <si>
     <t>Skill_Name_NeatAndTidy</t>
   </si>
   <si>
     <t>Skill_Desc_NeatAndTidy</t>
+  </si>
+  <si>
+    <t>Skill_Sweep</t>
+  </si>
+  <si>
+    <t>横扫</t>
+  </si>
+  <si>
+    <t>对英雄附近的敌人造成{0}伤害。</t>
+  </si>
+  <si>
+    <t>Skill_Name_Sweep</t>
+  </si>
+  <si>
+    <t>Skill_Desc_Sweep</t>
   </si>
 </sst>
 </file>
@@ -854,163 +884,163 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1332,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1" style="1"/>
@@ -1343,12 +1373,14 @@
     <col min="6" max="6" width="17.3333333333333" customWidth="1" style="1"/>
     <col min="7" max="10" width="20.8333333333333" customWidth="1" style="1"/>
     <col min="11" max="11" width="16.75" customWidth="1" style="1"/>
-    <col min="12" max="12" width="17.3333333333333" customWidth="1" style="1"/>
-    <col min="13" max="16" width="20.8333333333333" customWidth="1" style="1"/>
-    <col min="17" max="19" width="16.75" customWidth="1" style="1"/>
-    <col min="20" max="20" width="23.25" customWidth="1" style="1"/>
-    <col min="21" max="21" width="19.1583333333333" customWidth="1" style="1"/>
-    <col min="22" max="16384" width="8.875" customWidth="1" style="1"/>
+    <col min="12" max="12" width="8.875" customWidth="1" style="1"/>
+    <col min="13" max="13" width="8.875" customWidth="1" style="1"/>
+    <col min="14" max="14" width="17.3333333333333" customWidth="1" style="1"/>
+    <col min="15" max="18" width="20.8333333333333" customWidth="1" style="1"/>
+    <col min="19" max="21" width="16.75" customWidth="1" style="1"/>
+    <col min="22" max="22" width="23.25" customWidth="1" style="1"/>
+    <col min="23" max="23" width="19.1583333333333" customWidth="1" style="1"/>
+    <col min="24" max="16384" width="8.875" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1367,80 +1399,92 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="L1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="U1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="2"/>
     </row>
     <row r="2" ht="28.75">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1448,60 +1492,66 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>22</v>
+      <c r="V3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="28.75">
@@ -1510,61 +1560,67 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="56.75">
@@ -1573,22 +1629,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
       </c>
       <c r="G5" s="2">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2">
         <v>8</v>
@@ -1599,30 +1655,36 @@
       <c r="K5" s="2">
         <v>6</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="2">
         <v>10</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="O5" s="2">
-        <v>2</v>
-      </c>
+      <c r="O5" s="2"/>
       <c r="P5" s="2">
         <v>1</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="Q5" s="2">
+        <v>2</v>
+      </c>
+      <c r="R5" s="2">
+        <v>1</v>
+      </c>
+      <c r="S5" s="2"/>
       <c r="T5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="U5" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="W5" s="2"/>
     </row>
     <row r="6" ht="42.75">
       <c r="A6" s="2"/>
@@ -1630,16 +1692,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1652,28 +1714,34 @@
       <c r="K6" s="2">
         <v>8</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2">
+      <c r="L6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2">
         <v>1</v>
       </c>
-      <c r="P6" s="2">
+      <c r="R6" s="2">
         <v>1</v>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="S6" s="2"/>
       <c r="T6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="U6" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="W6" s="2"/>
     </row>
     <row r="7" ht="74" customHeight="1">
       <c r="A7" s="2"/>
@@ -1681,44 +1749,50 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
-        <v>1.8</v>
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
+      <c r="P7" s="2">
+        <v>2</v>
+      </c>
       <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="U7" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="W7" s="2"/>
     </row>
     <row r="8" ht="56.75">
       <c r="A8" s="2"/>
@@ -1726,19 +1800,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G8" s="2">
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1749,23 +1823,29 @@
         <v>10</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="U8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W8" s="2"/>
     </row>
     <row r="9" ht="70.75">
       <c r="A9" s="2"/>
@@ -1773,22 +1853,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F9" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -1799,34 +1879,40 @@
       <c r="K9" s="2">
         <v>10</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" s="2">
         <v>20</v>
       </c>
-      <c r="M9" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0.2</v>
-      </c>
       <c r="O9" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P9" s="2">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="Q9" s="2">
         <v>0.5</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>76</v>
+      <c r="R9" s="2">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.5</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="U9" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W9" s="2"/>
     </row>
     <row r="10" ht="28.75">
       <c r="A10" s="2"/>
@@ -1834,13 +1920,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2">
         <v>5</v>
@@ -1850,24 +1936,30 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2">
+      <c r="L10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N10" s="2">
         <v>4</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="U10" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="W10" s="2"/>
     </row>
     <row r="11" ht="42.75">
       <c r="A11" s="2"/>
@@ -1875,13 +1967,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2">
         <v>8</v>
@@ -1891,24 +1983,30 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2">
+      <c r="L11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N11" s="2">
         <v>4</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U11" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="W11" s="2"/>
     </row>
     <row r="12" ht="42.75">
       <c r="A12" s="2"/>
@@ -1916,17 +2014,17 @@
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F12" s="2"/>
       <c r="H12" s="2">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
@@ -1937,28 +2035,34 @@
       <c r="K12" s="2">
         <v>8</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="O12" s="2">
+      <c r="L12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Q12" s="2">
         <v>1</v>
       </c>
-      <c r="P12" s="2">
+      <c r="R12" s="2">
         <v>1</v>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U12" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="W12" s="2"/>
     </row>
     <row r="13" ht="42.75">
       <c r="A13" s="2"/>
@@ -1966,16 +2070,16 @@
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1983,96 +2087,143 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>98</v>
-      </c>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
       <c r="T13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="42.75">
+        <v>68</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" ht="56.75">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F14" s="2">
         <v>30</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2">
+      <c r="L14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N14" s="2">
         <v>15</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2">
+      <c r="O14" s="2"/>
+      <c r="P14" s="2">
         <v>0.5</v>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
       <c r="T14" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="U14" s="2"/>
-    </row>
-    <row r="15">
+        <v>68</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" ht="28.75">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="B15" s="2">
+        <v>11</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="2">
+        <v>50</v>
+      </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2">
+        <v>5</v>
+      </c>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="J15" s="2">
+        <v>3</v>
+      </c>
+      <c r="K15" s="2">
+        <v>10</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>30</v>
+      </c>
       <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
+      <c r="P15" s="2">
+        <v>1</v>
+      </c>
       <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="W15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -2091,6 +2242,8 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2"/>
@@ -2114,6 +2267,8 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2"/>
@@ -2137,6 +2292,8 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2"/>
@@ -2160,6 +2317,8 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2"/>
@@ -2183,6 +2342,8 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2"/>
@@ -2206,6 +2367,8 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2"/>
@@ -2229,6 +2392,8 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2"/>
@@ -2252,6 +2417,8 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2"/>
@@ -2275,6 +2442,8 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2"/>
@@ -2298,6 +2467,8 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2"/>
@@ -2321,6 +2492,8 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2"/>
@@ -2344,6 +2517,8 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2"/>
@@ -2367,6 +2542,8 @@
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
